--- a/artfynd/A 65217-2021 artfynd.xlsx
+++ b/artfynd/A 65217-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 65217-2021 artfynd.xlsx
+++ b/artfynd/A 65217-2021 artfynd.xlsx
@@ -678,11 +678,11 @@
         <v>90813251</v>
       </c>
       <c r="B2" t="n">
-        <v>56395</v>
+        <v>57320</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Ej möjlig att validera</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>494850.9151987299</v>
+        <v>494851</v>
       </c>
       <c r="R2" t="n">
-        <v>6647446.994046485</v>
+        <v>6647447</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -748,19 +748,9 @@
           <t>2020-09-23</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2020-09-23</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,11 +784,11 @@
         <v>90813252</v>
       </c>
       <c r="B3" t="n">
-        <v>56395</v>
+        <v>57320</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ej möjlig att validera</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -831,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>494822.749959293</v>
+        <v>494823</v>
       </c>
       <c r="R3" t="n">
-        <v>6647392.951655139</v>
+        <v>6647393</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -864,19 +854,9 @@
           <t>2020-09-23</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2020-09-23</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -910,11 +890,11 @@
         <v>90813253</v>
       </c>
       <c r="B4" t="n">
-        <v>56395</v>
+        <v>57320</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ej möjlig att validera</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -947,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>494816.2290929726</v>
+        <v>494816</v>
       </c>
       <c r="R4" t="n">
-        <v>6647392.960796161</v>
+        <v>6647393</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -980,19 +960,9 @@
           <t>2020-09-23</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2020-09-23</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 65217-2021 artfynd.xlsx
+++ b/artfynd/A 65217-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1141,6 +1141,470 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>121596552</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57356</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Behöver inte valideras</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Hörksälven, Vstm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>494915</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6647315</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-10-28</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-10-28</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Äldre blåbärsbarrblandskog vid bäck.</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>121596553</v>
+      </c>
+      <c r="B7" t="n">
+        <v>92031</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Hörksälven, Vstm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>494849</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6647448</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-10-28</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-10-28</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Äldre tallskog.</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>121596517</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57356</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Behöver inte valideras</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Hörksälven, Vstm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>494816</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6647395</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-10-29</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-10-29</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Äldre blåbärstallskog.</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>121596518</v>
+      </c>
+      <c r="B9" t="n">
+        <v>95399</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>2869</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Bollvitmossa</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Sphagnum wulfianum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Hörksälven, Vstm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>494817</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6647390</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-10-29</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-10-29</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Äldre tallsumpskog</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 65217-2021 artfynd.xlsx
+++ b/artfynd/A 65217-2021 artfynd.xlsx
@@ -1144,14 +1144,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121596552</v>
+        <v>121596553</v>
       </c>
       <c r="B6" t="n">
-        <v>57356</v>
+        <v>92031</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Behöver inte valideras</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1160,39 +1160,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>5966</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Hörksälven, Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>494915</v>
+        <v>494849</v>
       </c>
       <c r="R6" t="n">
-        <v>6647315</v>
+        <v>6647448</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1238,12 +1233,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Äldre blåbärsbarrblandskog vid bäck.</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>tall</t>
+          <t>Äldre tallskog.</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1265,10 +1255,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121596553</v>
+        <v>121596518</v>
       </c>
       <c r="B7" t="n">
-        <v>92031</v>
+        <v>95399</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1277,25 +1267,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5966</v>
+        <v>2869</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1305,10 +1295,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>494849</v>
+        <v>494817</v>
       </c>
       <c r="R7" t="n">
-        <v>6647448</v>
+        <v>6647390</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1335,12 +1325,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1354,7 +1344,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Äldre tallskog.</t>
+          <t>Äldre tallsumpskog</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1376,7 +1366,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121596517</v>
+        <v>121596552</v>
       </c>
       <c r="B8" t="n">
         <v>57356</v>
@@ -1421,10 +1411,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>494816</v>
+        <v>494915</v>
       </c>
       <c r="R8" t="n">
-        <v>6647395</v>
+        <v>6647315</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1451,12 +1441,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1470,7 +1460,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Äldre blåbärstallskog.</t>
+          <t>Äldre blåbärsbarrblandskog vid bäck.</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -1497,50 +1487,55 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121596518</v>
+        <v>121596517</v>
       </c>
       <c r="B9" t="n">
-        <v>95399</v>
+        <v>57356</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2869</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hörksälven, Vstm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>494817</v>
+        <v>494816</v>
       </c>
       <c r="R9" t="n">
-        <v>6647390</v>
+        <v>6647395</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1586,7 +1581,12 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Äldre tallsumpskog</t>
+          <t>Äldre blåbärstallskog.</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>tall</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>

--- a/artfynd/A 65217-2021 artfynd.xlsx
+++ b/artfynd/A 65217-2021 artfynd.xlsx
@@ -1144,14 +1144,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121596553</v>
+        <v>121596552</v>
       </c>
       <c r="B6" t="n">
-        <v>92031</v>
+        <v>57356</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1160,34 +1160,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5966</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Hörksälven, Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>494849</v>
+        <v>494915</v>
       </c>
       <c r="R6" t="n">
-        <v>6647448</v>
+        <v>6647315</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1233,7 +1238,12 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Äldre tallskog.</t>
+          <t>Äldre blåbärsbarrblandskog vid bäck.</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>tall</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1255,50 +1265,55 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121596518</v>
+        <v>121596517</v>
       </c>
       <c r="B7" t="n">
-        <v>95399</v>
+        <v>57356</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2869</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hörksälven, Vstm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>494817</v>
+        <v>494816</v>
       </c>
       <c r="R7" t="n">
-        <v>6647390</v>
+        <v>6647395</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1344,7 +1359,12 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Äldre tallsumpskog</t>
+          <t>Äldre blåbärstallskog.</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>tall</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1366,14 +1386,14 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121596552</v>
+        <v>121596553</v>
       </c>
       <c r="B8" t="n">
-        <v>57356</v>
+        <v>92031</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Behöver inte valideras</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1382,39 +1402,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>5966</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hörksälven, Vstm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>494915</v>
+        <v>494849</v>
       </c>
       <c r="R8" t="n">
-        <v>6647315</v>
+        <v>6647448</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1460,12 +1475,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Äldre blåbärsbarrblandskog vid bäck.</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>tall</t>
+          <t>Äldre tallskog.</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1487,55 +1497,50 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121596517</v>
+        <v>121596518</v>
       </c>
       <c r="B9" t="n">
-        <v>57356</v>
+        <v>95399</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Behöver inte valideras</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>2869</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hörksälven, Vstm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>494816</v>
+        <v>494817</v>
       </c>
       <c r="R9" t="n">
-        <v>6647395</v>
+        <v>6647390</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1581,12 +1586,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Äldre blåbärstallskog.</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>tall</t>
+          <t>Äldre tallsumpskog</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>

--- a/artfynd/A 65217-2021 artfynd.xlsx
+++ b/artfynd/A 65217-2021 artfynd.xlsx
@@ -1144,14 +1144,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121596552</v>
+        <v>121596553</v>
       </c>
       <c r="B6" t="n">
-        <v>57356</v>
+        <v>92031</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Behöver inte valideras</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1160,39 +1160,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>5966</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Hörksälven, Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>494915</v>
+        <v>494849</v>
       </c>
       <c r="R6" t="n">
-        <v>6647315</v>
+        <v>6647448</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1238,12 +1233,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Äldre blåbärsbarrblandskog vid bäck.</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>tall</t>
+          <t>Äldre tallskog.</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1265,55 +1255,50 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121596517</v>
+        <v>121596518</v>
       </c>
       <c r="B7" t="n">
-        <v>57356</v>
+        <v>95399</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Behöver inte valideras</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>2869</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hörksälven, Vstm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>494816</v>
+        <v>494817</v>
       </c>
       <c r="R7" t="n">
-        <v>6647395</v>
+        <v>6647390</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1359,12 +1344,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Äldre blåbärstallskog.</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>tall</t>
+          <t>Äldre tallsumpskog</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1386,14 +1366,14 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121596553</v>
+        <v>121596517</v>
       </c>
       <c r="B8" t="n">
-        <v>92031</v>
+        <v>57356</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1402,34 +1382,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5966</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hörksälven, Vstm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>494849</v>
+        <v>494816</v>
       </c>
       <c r="R8" t="n">
-        <v>6647448</v>
+        <v>6647395</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1456,12 +1441,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1475,7 +1460,12 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Äldre tallskog.</t>
+          <t>Äldre blåbärstallskog.</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>tall</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1497,50 +1487,55 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121596518</v>
+        <v>121596552</v>
       </c>
       <c r="B9" t="n">
-        <v>95399</v>
+        <v>57356</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2869</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hörksälven, Vstm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>494817</v>
+        <v>494915</v>
       </c>
       <c r="R9" t="n">
-        <v>6647390</v>
+        <v>6647315</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1567,12 +1562,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1586,7 +1581,12 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Äldre tallsumpskog</t>
+          <t>Äldre blåbärsbarrblandskog vid bäck.</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>tall</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>

--- a/artfynd/A 65217-2021 artfynd.xlsx
+++ b/artfynd/A 65217-2021 artfynd.xlsx
@@ -1265,10 +1265,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121596518</v>
+        <v>121596553</v>
       </c>
       <c r="B7" t="n">
-        <v>95407</v>
+        <v>92039</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1277,25 +1277,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2869</v>
+        <v>5966</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1305,10 +1305,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>494817</v>
+        <v>494849</v>
       </c>
       <c r="R7" t="n">
-        <v>6647390</v>
+        <v>6647448</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Äldre tallsumpskog</t>
+          <t>Äldre tallskog.</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1376,14 +1376,14 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121596553</v>
+        <v>121596517</v>
       </c>
       <c r="B8" t="n">
-        <v>92039</v>
+        <v>57357</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1392,34 +1392,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5966</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hörksälven, Vstm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>494849</v>
+        <v>494816</v>
       </c>
       <c r="R8" t="n">
-        <v>6647448</v>
+        <v>6647395</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1446,12 +1451,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1465,7 +1470,12 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Äldre tallskog.</t>
+          <t>Äldre blåbärstallskog.</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>tall</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1487,55 +1497,50 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121596517</v>
+        <v>121596518</v>
       </c>
       <c r="B9" t="n">
-        <v>57357</v>
+        <v>95407</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Behöver inte valideras</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>2869</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hörksälven, Vstm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>494816</v>
+        <v>494817</v>
       </c>
       <c r="R9" t="n">
-        <v>6647395</v>
+        <v>6647390</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1581,12 +1586,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Äldre blåbärstallskog.</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>tall</t>
+          <t>Äldre tallsumpskog</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>

--- a/artfynd/A 65217-2021 artfynd.xlsx
+++ b/artfynd/A 65217-2021 artfynd.xlsx
@@ -1144,14 +1144,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121596552</v>
+        <v>121596553</v>
       </c>
       <c r="B6" t="n">
-        <v>57357</v>
+        <v>92039</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Behöver inte valideras</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1160,39 +1160,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>5966</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Hörksälven, Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>494915</v>
+        <v>494849</v>
       </c>
       <c r="R6" t="n">
-        <v>6647315</v>
+        <v>6647448</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1238,12 +1233,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Äldre blåbärsbarrblandskog vid bäck.</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>tall</t>
+          <t>Äldre tallskog.</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1265,14 +1255,14 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121596553</v>
+        <v>121596552</v>
       </c>
       <c r="B7" t="n">
-        <v>92039</v>
+        <v>57357</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1281,34 +1271,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5966</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hörksälven, Vstm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>494849</v>
+        <v>494915</v>
       </c>
       <c r="R7" t="n">
-        <v>6647448</v>
+        <v>6647315</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1354,7 +1349,12 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Äldre tallskog.</t>
+          <t>Äldre blåbärsbarrblandskog vid bäck.</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>tall</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1376,55 +1376,50 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121596517</v>
+        <v>121596518</v>
       </c>
       <c r="B8" t="n">
-        <v>57357</v>
+        <v>95407</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Behöver inte valideras</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>2869</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hörksälven, Vstm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>494816</v>
+        <v>494817</v>
       </c>
       <c r="R8" t="n">
-        <v>6647395</v>
+        <v>6647390</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1470,12 +1465,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Äldre blåbärstallskog.</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>tall</t>
+          <t>Äldre tallsumpskog</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1497,50 +1487,55 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121596518</v>
+        <v>121596517</v>
       </c>
       <c r="B9" t="n">
-        <v>95407</v>
+        <v>57357</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2869</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hörksälven, Vstm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>494817</v>
+        <v>494816</v>
       </c>
       <c r="R9" t="n">
-        <v>6647390</v>
+        <v>6647395</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1586,7 +1581,12 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Äldre tallsumpskog</t>
+          <t>Äldre blåbärstallskog.</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>tall</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>

--- a/artfynd/A 65217-2021 artfynd.xlsx
+++ b/artfynd/A 65217-2021 artfynd.xlsx
@@ -1144,10 +1144,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121596553</v>
+        <v>121596518</v>
       </c>
       <c r="B6" t="n">
-        <v>92039</v>
+        <v>95407</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1156,25 +1156,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5966</v>
+        <v>2869</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1184,10 +1184,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>494849</v>
+        <v>494817</v>
       </c>
       <c r="R6" t="n">
-        <v>6647448</v>
+        <v>6647390</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1214,12 +1214,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1233,7 +1233,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Äldre tallskog.</t>
+          <t>Äldre tallsumpskog</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1376,10 +1376,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121596518</v>
+        <v>121596553</v>
       </c>
       <c r="B8" t="n">
-        <v>95407</v>
+        <v>92039</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1388,25 +1388,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2869</v>
+        <v>5966</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1416,10 +1416,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>494817</v>
+        <v>494849</v>
       </c>
       <c r="R8" t="n">
-        <v>6647390</v>
+        <v>6647448</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1446,12 +1446,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1465,7 +1465,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Äldre tallsumpskog</t>
+          <t>Äldre tallskog.</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>

--- a/artfynd/A 65217-2021 artfynd.xlsx
+++ b/artfynd/A 65217-2021 artfynd.xlsx
@@ -1144,50 +1144,55 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121596518</v>
+        <v>121596552</v>
       </c>
       <c r="B6" t="n">
-        <v>95407</v>
+        <v>57357</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2869</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Hörksälven, Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>494817</v>
+        <v>494915</v>
       </c>
       <c r="R6" t="n">
-        <v>6647390</v>
+        <v>6647315</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1214,12 +1219,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1233,7 +1238,12 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Äldre tallsumpskog</t>
+          <t>Äldre blåbärsbarrblandskog vid bäck.</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>tall</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1255,7 +1265,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121596552</v>
+        <v>121596517</v>
       </c>
       <c r="B7" t="n">
         <v>57357</v>
@@ -1300,10 +1310,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>494915</v>
+        <v>494816</v>
       </c>
       <c r="R7" t="n">
-        <v>6647315</v>
+        <v>6647395</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1330,12 +1340,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1349,7 +1359,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Äldre blåbärsbarrblandskog vid bäck.</t>
+          <t>Äldre blåbärstallskog.</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
@@ -1487,55 +1497,50 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121596517</v>
+        <v>121596518</v>
       </c>
       <c r="B9" t="n">
-        <v>57357</v>
+        <v>95407</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Behöver inte valideras</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>2869</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hörksälven, Vstm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>494816</v>
+        <v>494817</v>
       </c>
       <c r="R9" t="n">
-        <v>6647395</v>
+        <v>6647390</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1581,12 +1586,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Äldre blåbärstallskog.</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>tall</t>
+          <t>Äldre tallsumpskog</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>

--- a/artfynd/A 65217-2021 artfynd.xlsx
+++ b/artfynd/A 65217-2021 artfynd.xlsx
@@ -1144,55 +1144,50 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121596552</v>
+        <v>121596518</v>
       </c>
       <c r="B6" t="n">
-        <v>57357</v>
+        <v>95407</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Behöver inte valideras</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>2869</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Hörksälven, Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>494915</v>
+        <v>494817</v>
       </c>
       <c r="R6" t="n">
-        <v>6647315</v>
+        <v>6647390</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1219,12 +1214,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1238,12 +1233,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Äldre blåbärsbarrblandskog vid bäck.</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>tall</t>
+          <t>Äldre tallsumpskog</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1265,14 +1255,14 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121596517</v>
+        <v>121596553</v>
       </c>
       <c r="B7" t="n">
-        <v>57357</v>
+        <v>92039</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Behöver inte valideras</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1281,39 +1271,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>5966</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hörksälven, Vstm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>494816</v>
+        <v>494849</v>
       </c>
       <c r="R7" t="n">
-        <v>6647395</v>
+        <v>6647448</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1340,12 +1325,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1359,12 +1344,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Äldre blåbärstallskog.</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>tall</t>
+          <t>Äldre tallskog.</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1386,14 +1366,14 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121596553</v>
+        <v>121596552</v>
       </c>
       <c r="B8" t="n">
-        <v>92039</v>
+        <v>57357</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1402,34 +1382,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5966</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hörksälven, Vstm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>494849</v>
+        <v>494915</v>
       </c>
       <c r="R8" t="n">
-        <v>6647448</v>
+        <v>6647315</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1475,7 +1460,12 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Äldre tallskog.</t>
+          <t>Äldre blåbärsbarrblandskog vid bäck.</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>tall</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1497,50 +1487,55 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121596518</v>
+        <v>121596517</v>
       </c>
       <c r="B9" t="n">
-        <v>95407</v>
+        <v>57357</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2869</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hörksälven, Vstm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>494817</v>
+        <v>494816</v>
       </c>
       <c r="R9" t="n">
-        <v>6647390</v>
+        <v>6647395</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1586,7 +1581,12 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Äldre tallsumpskog</t>
+          <t>Äldre blåbärstallskog.</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>tall</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>

--- a/artfynd/A 65217-2021 artfynd.xlsx
+++ b/artfynd/A 65217-2021 artfynd.xlsx
@@ -1144,10 +1144,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121596518</v>
+        <v>121596553</v>
       </c>
       <c r="B6" t="n">
-        <v>95407</v>
+        <v>92039</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1156,25 +1156,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2869</v>
+        <v>5966</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1184,10 +1184,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>494817</v>
+        <v>494849</v>
       </c>
       <c r="R6" t="n">
-        <v>6647390</v>
+        <v>6647448</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1214,12 +1214,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1233,7 +1233,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Äldre tallsumpskog</t>
+          <t>Äldre tallskog.</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1255,14 +1255,14 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121596553</v>
+        <v>121596552</v>
       </c>
       <c r="B7" t="n">
-        <v>92039</v>
+        <v>57357</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1271,34 +1271,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5966</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hörksälven, Vstm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>494849</v>
+        <v>494915</v>
       </c>
       <c r="R7" t="n">
-        <v>6647448</v>
+        <v>6647315</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1344,7 +1349,12 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Äldre tallskog.</t>
+          <t>Äldre blåbärsbarrblandskog vid bäck.</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>tall</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1366,7 +1376,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121596552</v>
+        <v>121596517</v>
       </c>
       <c r="B8" t="n">
         <v>57357</v>
@@ -1411,10 +1421,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>494915</v>
+        <v>494816</v>
       </c>
       <c r="R8" t="n">
-        <v>6647315</v>
+        <v>6647395</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1441,12 +1451,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1460,7 +1470,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Äldre blåbärsbarrblandskog vid bäck.</t>
+          <t>Äldre blåbärstallskog.</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -1487,55 +1497,50 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121596517</v>
+        <v>121596518</v>
       </c>
       <c r="B9" t="n">
-        <v>57357</v>
+        <v>95407</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Behöver inte valideras</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>2869</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hörksälven, Vstm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>494816</v>
+        <v>494817</v>
       </c>
       <c r="R9" t="n">
-        <v>6647395</v>
+        <v>6647390</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1581,12 +1586,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Äldre blåbärstallskog.</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>tall</t>
+          <t>Äldre tallsumpskog</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>

--- a/artfynd/A 65217-2021 artfynd.xlsx
+++ b/artfynd/A 65217-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1606,6 +1606,205 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>128178727</v>
+      </c>
+      <c r="B10" t="n">
+        <v>96720</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>53</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Hörkälven , Vstm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>494915</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6647368</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-09-03</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-09-03</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Sparsamt på grov tallåga.</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Anton Björk, Niklas Trogen</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>128178602</v>
+      </c>
+      <c r="B11" t="n">
+        <v>92257</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>4745</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tallriska</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Lactarius musteus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Hörkälven , Vstm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>494848</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6647439</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-09-03</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-09-03</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Anton Björk, Niklas Trogen</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 65217-2021 artfynd.xlsx
+++ b/artfynd/A 65217-2021 artfynd.xlsx
@@ -1611,7 +1611,7 @@
         <v>128178727</v>
       </c>
       <c r="B10" t="n">
-        <v>96720</v>
+        <v>96721</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1713,7 +1713,7 @@
         <v>128178602</v>
       </c>
       <c r="B11" t="n">
-        <v>92257</v>
+        <v>92258</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 65217-2021 artfynd.xlsx
+++ b/artfynd/A 65217-2021 artfynd.xlsx
@@ -1611,7 +1611,7 @@
         <v>128178727</v>
       </c>
       <c r="B10" t="n">
-        <v>96721</v>
+        <v>96722</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1713,7 +1713,7 @@
         <v>128178602</v>
       </c>
       <c r="B11" t="n">
-        <v>92258</v>
+        <v>92259</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 65217-2021 artfynd.xlsx
+++ b/artfynd/A 65217-2021 artfynd.xlsx
@@ -1611,7 +1611,7 @@
         <v>128178727</v>
       </c>
       <c r="B10" t="n">
-        <v>96722</v>
+        <v>96730</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1713,7 +1713,7 @@
         <v>128178602</v>
       </c>
       <c r="B11" t="n">
-        <v>92259</v>
+        <v>92267</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 65217-2021 artfynd.xlsx
+++ b/artfynd/A 65217-2021 artfynd.xlsx
@@ -1611,7 +1611,7 @@
         <v>128178727</v>
       </c>
       <c r="B10" t="n">
-        <v>96730</v>
+        <v>96823</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1713,7 +1713,7 @@
         <v>128178602</v>
       </c>
       <c r="B11" t="n">
-        <v>92267</v>
+        <v>92359</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 65217-2021 artfynd.xlsx
+++ b/artfynd/A 65217-2021 artfynd.xlsx
@@ -1611,7 +1611,7 @@
         <v>128178727</v>
       </c>
       <c r="B10" t="n">
-        <v>96823</v>
+        <v>96835</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1713,7 +1713,7 @@
         <v>128178602</v>
       </c>
       <c r="B11" t="n">
-        <v>92359</v>
+        <v>92371</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 65217-2021 artfynd.xlsx
+++ b/artfynd/A 65217-2021 artfynd.xlsx
@@ -1611,7 +1611,7 @@
         <v>128178727</v>
       </c>
       <c r="B10" t="n">
-        <v>96835</v>
+        <v>96837</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1713,7 +1713,7 @@
         <v>128178602</v>
       </c>
       <c r="B11" t="n">
-        <v>92371</v>
+        <v>92373</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 65217-2021 artfynd.xlsx
+++ b/artfynd/A 65217-2021 artfynd.xlsx
@@ -1611,7 +1611,7 @@
         <v>128178727</v>
       </c>
       <c r="B10" t="n">
-        <v>96837</v>
+        <v>96838</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1713,7 +1713,7 @@
         <v>128178602</v>
       </c>
       <c r="B11" t="n">
-        <v>92373</v>
+        <v>92374</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 65217-2021 artfynd.xlsx
+++ b/artfynd/A 65217-2021 artfynd.xlsx
@@ -1611,7 +1611,7 @@
         <v>128178727</v>
       </c>
       <c r="B10" t="n">
-        <v>96838</v>
+        <v>96865</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1713,7 +1713,7 @@
         <v>128178602</v>
       </c>
       <c r="B11" t="n">
-        <v>92374</v>
+        <v>92401</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 65217-2021 artfynd.xlsx
+++ b/artfynd/A 65217-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>90813251</v>
+        <v>103432602</v>
       </c>
       <c r="B2" t="n">
-        <v>57348</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,45 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>med groddkorn</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hörkälven, Vstm</t>
+          <t>Hörksälven V om, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>494851</v>
+        <v>494860</v>
       </c>
       <c r="R2" t="n">
-        <v>6647447</v>
+        <v>6647334</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,12 +748,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2020-09-23</t>
+          <t>2022-09-07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2020-09-23</t>
+          <t>2022-09-07</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -759,37 +762,59 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Blandsumpskog</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>gran, glasbjörk, tall</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # murken låga  # Picea abies</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Länsstyrelsen i Örebro län, inventering</t>
-        </is>
-      </c>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>90813252</v>
+        <v>103466125</v>
       </c>
       <c r="B3" t="n">
-        <v>57348</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,34 +822,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>med groddkorn</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hörkälven, Vstm</t>
+          <t>Hörksälven, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>494823</v>
+        <v>494910</v>
       </c>
       <c r="R3" t="n">
-        <v>6647393</v>
+        <v>6647385</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -851,12 +884,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2020-09-23</t>
+          <t>2022-09-07</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2020-09-23</t>
+          <t>2022-09-07</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -865,37 +898,59 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Sandbarrskog</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>blåbärstyp</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # murknande tallåga  # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Länsstyrelsen i Örebro län, inventering</t>
-        </is>
-      </c>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>90813253</v>
+        <v>121596459</v>
       </c>
       <c r="B4" t="n">
-        <v>57348</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -903,37 +958,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>53</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hörkälven, Vstm</t>
+          <t>Hörksälven, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>494816</v>
+        <v>494962</v>
       </c>
       <c r="R4" t="n">
-        <v>6647393</v>
+        <v>6647357</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -957,12 +1012,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2020-09-23</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2020-09-23</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -973,16 +1028,26 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Äldre barrsumpskog vid bäck.</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>barrträdslåga</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Jenny Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Jenny Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -993,15 +1058,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>103466125</v>
+        <v>128178727</v>
       </c>
       <c r="B5" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,27 +1087,19 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>med groddkorn</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hörksälven, Vstm</t>
+          <t>Hörkälven , Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>494910.0182127542</v>
+        <v>494915</v>
       </c>
       <c r="R5" t="n">
-        <v>6647384.818252227</v>
+        <v>6647368</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1071,22 +1123,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-09-07</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-09-07</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-03</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Sparsamt på grov tallåga.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1095,104 +1142,63 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Sandbarrskog</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>blåbärstyp</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # murknande tallåga  # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Anton Björk, Niklas Trogen</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121596517</v>
+        <v>121596518</v>
       </c>
       <c r="B6" t="n">
-        <v>57365</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>97231</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>2869</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Hörksälven, Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>494816</v>
+        <v>494817</v>
       </c>
       <c r="R6" t="n">
-        <v>6647395</v>
+        <v>6647390</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1238,12 +1244,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Äldre blåbärstallskog.</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>tall</t>
+          <t>Äldre tallsumpskog</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1265,15 +1266,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121596553</v>
+        <v>128178602</v>
       </c>
       <c r="B7" t="n">
-        <v>92053</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92841</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1281,37 +1277,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5966</v>
+        <v>4745</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Hörksälven, Vstm</t>
+          <t>Hörkälven , Vstm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>494849</v>
+        <v>494848</v>
       </c>
       <c r="R7" t="n">
-        <v>6647448</v>
+        <v>6647439</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1335,12 +1331,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1351,40 +1347,26 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>Äldre tallskog.</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Jenny Andersson</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Jenny Andersson</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>Länsstyrelsen i Örebro län, inventering</t>
-        </is>
-      </c>
+          <t>Anton Björk, Niklas Trogen</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121596552</v>
+        <v>121596553</v>
       </c>
       <c r="B8" t="n">
-        <v>57365</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1392,39 +1374,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>5966</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hörksälven, Vstm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>494915</v>
+        <v>494849</v>
       </c>
       <c r="R8" t="n">
-        <v>6647315</v>
+        <v>6647448</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1470,12 +1447,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Äldre blåbärsbarrblandskog vid bäck.</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>tall</t>
+          <t>Äldre tallskog.</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1497,53 +1469,48 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121596518</v>
+        <v>90813251</v>
       </c>
       <c r="B9" t="n">
-        <v>95425</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2869</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Hörksälven, Vstm</t>
+          <t>Hörkälven, Vstm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>494817</v>
+        <v>494851</v>
       </c>
       <c r="R9" t="n">
-        <v>6647390</v>
+        <v>6647447</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1567,12 +1534,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2020-09-23</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2020-09-23</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1583,21 +1550,16 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>Äldre tallsumpskog</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Jenny Andersson</t>
+          <t>Jesper Hansson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Jenny Andersson</t>
+          <t>Jesper Hansson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1608,10 +1570,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128178727</v>
+        <v>90813252</v>
       </c>
       <c r="B10" t="n">
-        <v>96865</v>
+        <v>57953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1619,37 +1581,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>53</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Hörkälven , Vstm</t>
+          <t>Hörkälven, Vstm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>494915</v>
+        <v>494823</v>
       </c>
       <c r="R10" t="n">
-        <v>6647368</v>
+        <v>6647393</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1673,17 +1635,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2020-09-23</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Sparsamt på grov tallåga.</t>
+          <t>2020-09-23</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1698,22 +1655,26 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Jesper Hansson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Anton Björk, Niklas Trogen</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr"/>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128178602</v>
+        <v>90813253</v>
       </c>
       <c r="B11" t="n">
-        <v>92401</v>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1721,37 +1682,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4745</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Hörkälven , Vstm</t>
+          <t>Hörkälven, Vstm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>494848</v>
+        <v>494816</v>
       </c>
       <c r="R11" t="n">
-        <v>6647439</v>
+        <v>6647393</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1775,12 +1736,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2020-09-23</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2020-09-23</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1795,15 +1756,251 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Jesper Hansson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anton Björk, Niklas Trogen</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr"/>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>121596517</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Hörksälven, Vstm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>494816</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6647395</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-10-29</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-10-29</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Äldre blåbärstallskog.</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>121596552</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Hörksälven, Vstm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>494915</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6647315</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-10-28</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-10-28</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Äldre blåbärsbarrblandskog vid bäck.</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 65217-2021 artfynd.xlsx
+++ b/artfynd/A 65217-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -808,6 +813,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103432602</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -944,6 +954,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103466125</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1055,6 +1070,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121596459</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1157,6 +1177,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128178727</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1263,6 +1288,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121596518</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1360,6 +1390,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128178602</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1466,6 +1501,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121596553</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1567,6 +1607,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90813251</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1668,6 +1713,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90813252</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1769,6 +1819,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90813253</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1885,6 +1940,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121596517</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2001,8 +2061,27 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121596552</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>